--- a/data.mn/public/datasets/meat-production-by-region-mn.xlsx
+++ b/data.mn/public/datasets/meat-production-by-region-mn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Өгөгдөл" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Өгөгдөл" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,44 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Баруун бүс</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Зүүн бүс</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Төвийн бүс</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Улаанбаатар</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Хангайн бүс</t>
         </is>
@@ -653,19 +633,19 @@
         <v>2019</v>
       </c>
       <c r="B11" t="n">
-        <v>113413.6</v>
+        <v>113413</v>
       </c>
       <c r="C11" t="n">
-        <v>95406.10000000001</v>
+        <v>95405.7</v>
       </c>
       <c r="D11" t="n">
-        <v>125109.2</v>
+        <v>120970.8</v>
       </c>
       <c r="E11" t="n">
         <v>8094.4</v>
       </c>
       <c r="F11" t="n">
-        <v>203005.9</v>
+        <v>205933.2</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +653,19 @@
         <v>2020</v>
       </c>
       <c r="B12" t="n">
-        <v>159589.1</v>
+        <v>159588.5</v>
       </c>
       <c r="C12" t="n">
-        <v>106995.4</v>
+        <v>106995</v>
       </c>
       <c r="D12" t="n">
-        <v>156941.4</v>
+        <v>152123.5</v>
       </c>
       <c r="E12" t="n">
         <v>7410.6</v>
       </c>
       <c r="F12" t="n">
-        <v>313579.5</v>
+        <v>320043.4</v>
       </c>
     </row>
     <row r="13">
@@ -693,19 +673,19 @@
         <v>2021</v>
       </c>
       <c r="B13" t="n">
-        <v>102702.7</v>
+        <v>102702.1</v>
       </c>
       <c r="C13" t="n">
-        <v>84610.10000000001</v>
+        <v>84609.7</v>
       </c>
       <c r="D13" t="n">
-        <v>141665.8</v>
+        <v>135806</v>
       </c>
       <c r="E13" t="n">
         <v>9341.299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>174359.3</v>
+        <v>174511.1</v>
       </c>
     </row>
     <row r="14">
@@ -713,19 +693,19 @@
         <v>2022</v>
       </c>
       <c r="B14" t="n">
-        <v>169011.8</v>
+        <v>169011.3</v>
       </c>
       <c r="C14" t="n">
-        <v>106085.5</v>
+        <v>106085.2</v>
       </c>
       <c r="D14" t="n">
-        <v>164404.8</v>
+        <v>158188.1</v>
       </c>
       <c r="E14" t="n">
-        <v>9161.299999999999</v>
+        <v>9161.200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>205303.2</v>
+        <v>207700.1</v>
       </c>
     </row>
     <row r="15">
@@ -733,19 +713,19 @@
         <v>2023</v>
       </c>
       <c r="B15" t="n">
-        <v>109642.8</v>
+        <v>114859.6</v>
       </c>
       <c r="C15" t="n">
-        <v>115241.4</v>
+        <v>128377.4</v>
       </c>
       <c r="D15" t="n">
-        <v>173757.3</v>
+        <v>187717.5</v>
       </c>
       <c r="E15" t="n">
-        <v>6492.6</v>
+        <v>6719.1</v>
       </c>
       <c r="F15" t="n">
-        <v>216948.7</v>
+        <v>230885.7</v>
       </c>
     </row>
     <row r="16">
@@ -753,19 +733,39 @@
         <v>2024</v>
       </c>
       <c r="B16" t="n">
-        <v>88604.10000000001</v>
+        <v>87262.89999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>58589</v>
+        <v>66796.7</v>
       </c>
       <c r="D16" t="n">
-        <v>121646.6</v>
+        <v>116421.5</v>
       </c>
       <c r="E16" t="n">
-        <v>5149.7</v>
+        <v>6410.1</v>
       </c>
       <c r="F16" t="n">
-        <v>176453.7</v>
+        <v>176245.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>169211.179</v>
+      </c>
+      <c r="C17" t="n">
+        <v>94900.167</v>
+      </c>
+      <c r="D17" t="n">
+        <v>167509.088</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2588.572</v>
+      </c>
+      <c r="F17" t="n">
+        <v>265663.375</v>
       </c>
     </row>
   </sheetData>
